--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-10.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -836,15 +836,19 @@
       <c r="K5" t="n">
         <v>1.54</v>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -868,6 +872,420 @@
       </c>
       <c r="T5" t="n">
         <v>34.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>English Sky Bet League 1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Stockport x Barnsley</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Stockport</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Barnsley</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>6</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>466</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>200</v>
+      </c>
+      <c r="S6" t="n">
+        <v>40</v>
+      </c>
+      <c r="T6" t="n">
+        <v>38.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FC Halifax Town x Gateshead</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>FC Halifax Town</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gateshead</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>AO Home Win</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>200</v>
+      </c>
+      <c r="S7" t="n">
+        <v>40</v>
+      </c>
+      <c r="T7" t="n">
+        <v>38.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Turkish 1 Lig</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Kayserispor x Manisa FK</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Kayserispor</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Manisa FK</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>337</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>200</v>
+      </c>
+      <c r="S8" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="T8" t="n">
+        <v>39.79</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Norwegian Eliteserien</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Rosenborg x Sandefjord</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Rosenborg</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>200</v>
+      </c>
+      <c r="S9" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="T9" t="n">
+        <v>35.37</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Ironi Tiberias x Hapoel Be'er Sheva</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ironi Tiberias</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Hapoel Be'er Sheva</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>352</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>200</v>
+      </c>
+      <c r="S10" t="n">
+        <v>40.82</v>
+      </c>
+      <c r="T10" t="n">
+        <v>38.98</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-10.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -922,15 +922,19 @@
       <c r="K6" t="n">
         <v>1.4</v>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1090,15 +1094,19 @@
       <c r="K8" t="n">
         <v>1.4</v>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1172,15 +1180,19 @@
       <c r="K9" t="n">
         <v>1.34</v>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1254,15 +1266,19 @@
       <c r="K10" t="n">
         <v>1.4</v>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1286,6 +1302,588 @@
       </c>
       <c r="T10" t="n">
         <v>38.98</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Belgian Pro League</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>RAAL La Louviere x Club Brugge</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAAL La Louviere</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Club Brugge</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>AO Away Win</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>699</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>200</v>
+      </c>
+      <c r="S11" t="n">
+        <v>42.55</v>
+      </c>
+      <c r="T11" t="n">
+        <v>40.64</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Hapoel Kiryat Shmona x Hapoel Tel Aviv</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Hapoel Kiryat Shmona</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Hapoel Tel Aviv</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>200</v>
+      </c>
+      <c r="S12" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="T12" t="n">
+        <v>31.83</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Greek Super League</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AEK Athens x OFI</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AEK Athens</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>OFI</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>1601</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>200</v>
+      </c>
+      <c r="S13" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="T13" t="n">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Portuguese Primeira Liga</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Maritimo x Porto</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Maritimo</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>1428</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>200</v>
+      </c>
+      <c r="S14" t="n">
+        <v>43.48</v>
+      </c>
+      <c r="T14" t="n">
+        <v>41.52</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Serbian Super League</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>FK Radnicki 1923 x Crvena Zvezda</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>FK Radnicki 1923</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Crvena Zvezda</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>7</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>224</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>200</v>
+      </c>
+      <c r="S15" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="T15" t="n">
+        <v>31.83</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>French Ligue 2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>St Etienne x Rodez</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rodez</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>797</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>200</v>
+      </c>
+      <c r="S16" t="n">
+        <v>42.55</v>
+      </c>
+      <c r="T16" t="n">
+        <v>40.64</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Dutch Eredivisie</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard x FC Twente</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>7</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>4059</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>200</v>
+      </c>
+      <c r="S17" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="T17" t="n">
+        <v>31.83</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-10.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T17"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1524,15 +1524,19 @@
       <c r="K13" t="n">
         <v>1.3</v>
       </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1606,15 +1610,19 @@
       <c r="K14" t="n">
         <v>1.33</v>
       </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1688,15 +1696,19 @@
       <c r="K15" t="n">
         <v>1.52</v>
       </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1770,15 +1782,19 @@
       <c r="K16" t="n">
         <v>1.4</v>
       </c>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1852,15 +1868,19 @@
       <c r="K17" t="n">
         <v>1.49</v>
       </c>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1884,6 +1904,342 @@
       </c>
       <c r="T17" t="n">
         <v>31.83</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Spanish La Liga</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Real Madrid x Villarreal</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>17152</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>200</v>
+      </c>
+      <c r="S18" t="n">
+        <v>38.46</v>
+      </c>
+      <c r="T18" t="n">
+        <v>36.73</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Dutch Eredivisie</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Ajax x NEC Nijmegen</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Ajax</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NEC Nijmegen</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>786</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>200</v>
+      </c>
+      <c r="S19" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="T19" t="n">
+        <v>35.37</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Vasco Da Gama x Remo</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Vasco Da Gama</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>2125</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="R20" t="n">
+        <v>200</v>
+      </c>
+      <c r="S20" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="T20" t="n">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Penarol x Progreso</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Penarol</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Progreso</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>218</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="R21" t="n">
+        <v>200</v>
+      </c>
+      <c r="S21" t="n">
+        <v>43.48</v>
+      </c>
+      <c r="T21" t="n">
+        <v>41.52</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-10.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,26 +509,6 @@
           <t>Liquidez_Lay</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Hora_Str</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Risco_Red_R$</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Stake_Sugerida_R$</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Lucro_Green_R$</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -601,20 +581,6 @@
       <c r="P2" t="n">
         <v>580</v>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>05:35</t>
-        </is>
-      </c>
-      <c r="R2" t="n">
-        <v>200</v>
-      </c>
-      <c r="S2" t="n">
-        <v>38.46</v>
-      </c>
-      <c r="T2" t="n">
-        <v>36.73</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -687,20 +653,6 @@
       <c r="P3" t="n">
         <v>279</v>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="R3" t="n">
-        <v>200</v>
-      </c>
-      <c r="S3" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="T3" t="n">
-        <v>31.83</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -773,20 +725,6 @@
       <c r="P4" t="n">
         <v>956</v>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="R4" t="n">
-        <v>200</v>
-      </c>
-      <c r="S4" t="n">
-        <v>34.48</v>
-      </c>
-      <c r="T4" t="n">
-        <v>32.93</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -859,20 +797,6 @@
       <c r="P5" t="n">
         <v>240</v>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="R5" t="n">
-        <v>200</v>
-      </c>
-      <c r="S5" t="n">
-        <v>35.71</v>
-      </c>
-      <c r="T5" t="n">
-        <v>34.1</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -945,20 +869,6 @@
       <c r="P6" t="n">
         <v>466</v>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="R6" t="n">
-        <v>200</v>
-      </c>
-      <c r="S6" t="n">
-        <v>40</v>
-      </c>
-      <c r="T6" t="n">
-        <v>38.2</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1031,20 +941,6 @@
       <c r="P7" t="n">
         <v>90</v>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="R7" t="n">
-        <v>200</v>
-      </c>
-      <c r="S7" t="n">
-        <v>40</v>
-      </c>
-      <c r="T7" t="n">
-        <v>38.2</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1117,20 +1013,6 @@
       <c r="P8" t="n">
         <v>337</v>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="R8" t="n">
-        <v>200</v>
-      </c>
-      <c r="S8" t="n">
-        <v>41.67</v>
-      </c>
-      <c r="T8" t="n">
-        <v>39.79</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1203,20 +1085,6 @@
       <c r="P9" t="n">
         <v>83</v>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="R9" t="n">
-        <v>200</v>
-      </c>
-      <c r="S9" t="n">
-        <v>37.04</v>
-      </c>
-      <c r="T9" t="n">
-        <v>35.37</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1289,20 +1157,6 @@
       <c r="P10" t="n">
         <v>352</v>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="R10" t="n">
-        <v>200</v>
-      </c>
-      <c r="S10" t="n">
-        <v>40.82</v>
-      </c>
-      <c r="T10" t="n">
-        <v>38.98</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1375,20 +1229,6 @@
       <c r="P11" t="n">
         <v>699</v>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="R11" t="n">
-        <v>200</v>
-      </c>
-      <c r="S11" t="n">
-        <v>42.55</v>
-      </c>
-      <c r="T11" t="n">
-        <v>40.64</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1461,20 +1301,6 @@
       <c r="P12" t="n">
         <v>115</v>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="R12" t="n">
-        <v>200</v>
-      </c>
-      <c r="S12" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="T12" t="n">
-        <v>31.83</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1547,20 +1373,6 @@
       <c r="P13" t="n">
         <v>1601</v>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="R13" t="n">
-        <v>200</v>
-      </c>
-      <c r="S13" t="n">
-        <v>35.71</v>
-      </c>
-      <c r="T13" t="n">
-        <v>34.1</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1633,20 +1445,6 @@
       <c r="P14" t="n">
         <v>1428</v>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="R14" t="n">
-        <v>200</v>
-      </c>
-      <c r="S14" t="n">
-        <v>43.48</v>
-      </c>
-      <c r="T14" t="n">
-        <v>41.52</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1719,20 +1517,6 @@
       <c r="P15" t="n">
         <v>224</v>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="R15" t="n">
-        <v>200</v>
-      </c>
-      <c r="S15" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="T15" t="n">
-        <v>31.83</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1805,20 +1589,6 @@
       <c r="P16" t="n">
         <v>797</v>
       </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="R16" t="n">
-        <v>200</v>
-      </c>
-      <c r="S16" t="n">
-        <v>42.55</v>
-      </c>
-      <c r="T16" t="n">
-        <v>40.64</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1891,20 +1661,6 @@
       <c r="P17" t="n">
         <v>4059</v>
       </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="R17" t="n">
-        <v>200</v>
-      </c>
-      <c r="S17" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="T17" t="n">
-        <v>31.83</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1977,20 +1733,6 @@
       <c r="P18" t="n">
         <v>17152</v>
       </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="R18" t="n">
-        <v>200</v>
-      </c>
-      <c r="S18" t="n">
-        <v>38.46</v>
-      </c>
-      <c r="T18" t="n">
-        <v>36.73</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2063,20 +1805,6 @@
       <c r="P19" t="n">
         <v>786</v>
       </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="R19" t="n">
-        <v>200</v>
-      </c>
-      <c r="S19" t="n">
-        <v>37.04</v>
-      </c>
-      <c r="T19" t="n">
-        <v>35.37</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2126,15 +1854,19 @@
       <c r="K20" t="n">
         <v>1.3</v>
       </c>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2145,20 +1877,6 @@
       <c r="P20" t="n">
         <v>2125</v>
       </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="R20" t="n">
-        <v>200</v>
-      </c>
-      <c r="S20" t="n">
-        <v>35.71</v>
-      </c>
-      <c r="T20" t="n">
-        <v>34.1</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2208,15 +1926,19 @@
       <c r="K21" t="n">
         <v>1.36</v>
       </c>
-      <c r="L21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2227,19 +1949,141 @@
       <c r="P21" t="n">
         <v>218</v>
       </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="R21" t="n">
-        <v>200</v>
-      </c>
-      <c r="S21" t="n">
-        <v>43.48</v>
-      </c>
-      <c r="T21" t="n">
-        <v>41.52</v>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>US MLS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Inter Miami CF x DC Utd</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Inter Miami CF</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>DC Utd</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>US MLS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Philadelphia x Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>1498</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-10.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-10.xlsx
@@ -1998,15 +1998,19 @@
       <c r="K22" t="n">
         <v>1.4</v>
       </c>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>AO Home Win</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2066,15 +2070,19 @@
       <c r="K23" t="n">
         <v>1.39</v>
       </c>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
